--- a/Tables/G_AbilityInfoTable.xlsx
+++ b/Tables/G_AbilityInfoTable.xlsx
@@ -341,7 +341,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
+    <col customWidth="1" min="1" max="26" width="12.63"/>
   </cols>
   <sheetData/>
   <drawing r:id="rId1"/>
@@ -356,10 +356,15 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="13.5"/>
-    <col customWidth="1" min="2" max="5" width="12.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="9.63"/>
     <col customWidth="1" min="6" max="7" width="13.0"/>
     <col customWidth="1" min="8" max="8" width="16.25"/>
-    <col customWidth="1" min="9" max="9" width="12.63"/>
+    <col customWidth="1" min="9" max="9" width="3.25"/>
+    <col customWidth="1" min="10" max="10" width="7.13"/>
+    <col customWidth="1" min="11" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6571,10 +6576,15 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="13.5"/>
-    <col customWidth="1" min="2" max="5" width="12.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="9.63"/>
     <col customWidth="1" min="6" max="7" width="13.0"/>
     <col customWidth="1" min="8" max="8" width="16.25"/>
-    <col customWidth="1" min="9" max="9" width="12.63"/>
+    <col customWidth="1" min="9" max="9" width="3.25"/>
+    <col customWidth="1" min="10" max="10" width="7.13"/>
+    <col customWidth="1" min="11" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12786,10 +12796,15 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="14.88"/>
-    <col customWidth="1" min="2" max="5" width="12.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="9.63"/>
     <col customWidth="1" min="6" max="7" width="13.0"/>
     <col customWidth="1" min="8" max="8" width="16.25"/>
-    <col customWidth="1" min="9" max="9" width="12.63"/>
+    <col customWidth="1" min="9" max="9" width="3.25"/>
+    <col customWidth="1" min="10" max="10" width="7.13"/>
+    <col customWidth="1" min="11" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19001,10 +19016,15 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="17.75"/>
-    <col customWidth="1" min="2" max="5" width="12.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="9.63"/>
     <col customWidth="1" min="6" max="7" width="13.0"/>
     <col customWidth="1" min="8" max="8" width="16.25"/>
-    <col customWidth="1" min="9" max="9" width="12.63"/>
+    <col customWidth="1" min="9" max="9" width="3.25"/>
+    <col customWidth="1" min="10" max="10" width="7.13"/>
+    <col customWidth="1" min="11" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
